--- a/samples/AI眼镜配件/成品-退货/A款-防滑鼻托套装(2对装)_退货分析.xlsx
+++ b/samples/AI眼镜配件/成品-退货/A款-防滑鼻托套装(2对装)_退货分析.xlsx
@@ -1739,7 +1739,7 @@
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>安心感(夸)</t>
+          <t>戴稳踏实感(夸)</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -2899,7 +2899,7 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -3557,7 +3557,7 @@
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -5359,7 +5359,7 @@
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr">
@@ -5647,7 +5647,7 @@
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr">
@@ -6079,7 +6079,7 @@
       <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr">
@@ -6375,7 +6375,7 @@
       <c r="L75" s="5" t="inlineStr"/>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr">
@@ -7243,7 +7243,7 @@
       <c r="L87" s="5" t="inlineStr"/>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr">
@@ -8870,11 +8870,11 @@
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="C63" s="11">
-        <f>SUMPRODUCT(--ISNUMBER(SEARCH("外观体面度",'01_打标明细'!$M$2:$M$95)))</f>
+        <f>SUMPRODUCT(--ISNUMBER(SEARCH("外观自然度",'01_打标明细'!$M$2:$M$95)))</f>
         <v/>
       </c>
       <c r="D63" s="12">
@@ -8930,11 +8930,11 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>安心感(夸)</t>
+          <t>戴稳踏实感(夸)</t>
         </is>
       </c>
       <c r="C66" s="11">
-        <f>SUMPRODUCT(--ISNUMBER(SEARCH("安心感(夸)",'01_打标明细'!$M$2:$M$95)))</f>
+        <f>SUMPRODUCT(--ISNUMBER(SEARCH("戴稳踏实感(夸)",'01_打标明细'!$M$2:$M$95)))</f>
         <v/>
       </c>
       <c r="D66" s="12">
